--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:41:23+00:00</t>
+    <t>2026-09-15T14:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:01:05+00:00</t>
+    <t>2026-09-15T17:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T17:45:52+00:00</t>
+    <t>2026-09-15T20:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T20:38:45+00:00</t>
+    <t>2026-09-16T05:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:15:10+00:00</t>
+    <t>2026-09-16T08:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:10:08+00:00</t>
+    <t>2026-09-17T08:26:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T08:26:08+00:00</t>
+    <t>2026-09-17T12:53:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-ect-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:53:08+00:00</t>
+    <t>2026-09-23T08:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
